--- a/docs/gift-finder-tags.xlsx
+++ b/docs/gift-finder-tags.xlsx
@@ -662,12 +662,12 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>생일·기념일에 향까지 함께 전하고 싶을 때</t>
+          <t>생일·기념일에 은은한 꽃 향까지 함께 전하고 싶을 때</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>비누로 만든 꽃송이라 은은한 향이 함께 나요. 향이 부담스러우면 무향 옵션도 있습니다.</t>
+          <t>비누로 빚은 꽃송이에 테차가 은은한 향을 더해 보내드려요. 향이 부담스러우면 주문 시 배송 요청 란에 "향 제거"나 "향 조금"이라고 적어주시면 그렇게 만들어 드려요.</t>
         </is>
       </c>
       <c r="I5" s="2" t="n"/>
